--- a/artfynd/A 35946-2023 artfynd.xlsx
+++ b/artfynd/A 35946-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35946-2023 artfynd.xlsx
+++ b/artfynd/A 35946-2023 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>118494608</v>
       </c>
       <c r="B4" t="n">
-        <v>106244</v>
+        <v>106251</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 35946-2023 artfynd.xlsx
+++ b/artfynd/A 35946-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95551846</v>
+        <v>67573796</v>
       </c>
       <c r="B2" t="n">
-        <v>104525</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107644</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,24 +703,35 @@
           <t>Wallr.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hagalund, Nrk</t>
+          <t>Björkängen, Pålsboda, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517529.67429647</v>
+        <v>517532</v>
       </c>
       <c r="R2" t="n">
-        <v>6548673.29795643</v>
+        <v>6548664</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,27 +755,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
+          <t>2017-09-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
+          <t>2017-09-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Känd förekomst.</t>
+          <t>Tillsammans med borsttistel i en vägslänt (norr om vägen). Vägrenen har slagits under högsommaren men plantorna har precis undgått att bli avslagna. Den ena plantan:46 cm hög, axet längd 10 cm, axets bredd 4 cm, stjälkens tjocklek 0,8 cm.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,34 +784,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niklas Hjort</t>
+          <t>Arne Holmer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niklas Hjort, Håkan Lernefalk</t>
+          <t>Arne Holmer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96236809</v>
+        <v>95551846</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107644</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>1129</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tistelsnyltrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Orobanche reticulata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,17 +837,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hagalund, Sköllersta, Nrk</t>
+          <t>Hagalund, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517529.67429647</v>
+        <v>517530</v>
       </c>
       <c r="R3" t="n">
-        <v>6548673.29795643</v>
+        <v>6548673</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Känd förekomst.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,27 +907,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Niklas Hjort</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk, Niklas Hjort</t>
+          <t>Niklas Hjort, Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118494608</v>
+        <v>118198070</v>
       </c>
       <c r="B4" t="n">
-        <v>106256</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107644</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,21 +957,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björkängen (Björkängen), Nrk</t>
+          <t>Hagalund, Hagalund, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517526</v>
+        <v>517528</v>
       </c>
       <c r="R4" t="n">
-        <v>6548683</v>
+        <v>6548687</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,12 +996,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,6 +1020,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1027,6 +1036,430 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118494608</v>
+      </c>
+      <c r="B5" t="n">
+        <v>107644</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1129</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tistelsnyltrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Orobanche reticulata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Björkängen, Björkängen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>517526</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6548683</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>72265885</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björkängen, Pålsboda, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>517532</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6548664</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-07-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-07-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Arne Holmer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Arne Holmer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>67578682</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björkängen, Pålsboda, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>517532</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6548664</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-09-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-09-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Arne Holmer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Arne Holmer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>96236809</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hagalund, Sköllersta, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>517530</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6548673</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-08-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-08-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Håkan Lernefalk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Niklas Hjort, Håkan Lernefalk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35946-2023 artfynd.xlsx
+++ b/artfynd/A 35946-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67573796</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95551846</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1036,6 +1051,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118198070</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1147,6 +1167,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118494608</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,6 +1286,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048412</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049870</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1471,6 +1506,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049957</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1585,6 +1625,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72265885</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1682,6 +1727,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67578682</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1784,6 +1834,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96236809</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1886,8 +1941,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135049951</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 35946-2023 artfynd.xlsx
+++ b/artfynd/A 35946-2023 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>135048412</v>
       </c>
       <c r="B6" t="n">
-        <v>107725</v>
+        <v>107780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>135049870</v>
       </c>
       <c r="B7" t="n">
-        <v>43224</v>
+        <v>43229</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>135049957</v>
       </c>
       <c r="B8" t="n">
-        <v>56904</v>
+        <v>56909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>135049951</v>
       </c>
       <c r="B12" t="n">
-        <v>104362</v>
+        <v>104415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 35946-2023 artfynd.xlsx
+++ b/artfynd/A 35946-2023 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>135048412</v>
       </c>
       <c r="B6" t="n">
-        <v>107780</v>
+        <v>107807</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>135049951</v>
       </c>
       <c r="B12" t="n">
-        <v>104415</v>
+        <v>104442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
